--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -1423,19 +1423,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1533,7 +1533,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1613,7 +1613,7 @@
         <v>206.6988</v>
       </c>
       <c r="P4" t="n">
-        <v>9.301446</v>
+        <v>9.301446000000002</v>
       </c>
       <c r="Q4" t="n">
         <v>0.04500000000000001</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>27.12358500000006</v>
+        <v>27.12358500000005</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>4.973799150320701e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>4.263256414560601e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>22.70240149999999</v>
+        <v>22.7024015</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>292.4524015</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>0.7498779525641024</v>
@@ -8184,10 +8184,10 @@
         <v>16.6988</v>
       </c>
       <c r="M14" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="N14" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -8559,10 +8559,10 @@
         <v>80.8169</v>
       </c>
       <c r="M19" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="N19" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97.54759850000006</v>
+        <v>97.54759850000005</v>
       </c>
     </row>
     <row r="9">

--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>2 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -638,7 +782,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -653,7 +797,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -671,7 +815,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -686,7 +830,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -703,7 +847,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -718,7 +862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -735,7 +879,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -750,7 +894,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -767,7 +911,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -782,7 +926,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -799,7 +943,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -814,7 +958,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -831,7 +975,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -846,7 +990,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -863,7 +1007,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,7 +1022,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -895,7 +1039,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -910,7 +1054,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -927,7 +1071,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -942,7 +1086,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -959,7 +1103,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -974,7 +1118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -991,7 +1135,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1006,7 +1150,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1167,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1038,7 +1182,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1199,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1070,7 +1214,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1231,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1102,7 +1246,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1263,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1134,7 +1278,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1295,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1166,7 +1310,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1327,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1198,7 +1342,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1359,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1230,7 +1374,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1391,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1262,7 +1406,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -9983,7 +10127,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2040: total service level 0.7499 &lt; 0.97 (shortage 97.548 t)</t>
+          <t>2040: общий уровень сервиса 0.7499 &lt; 0.97 (дефицит 97.548 т)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10022,7 +10166,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2040-01: physical stock 5.952 t &lt; 45-day reserve 48.082 t</t>
+          <t>2040-01: физический запас 5.952 т &lt; 45-дневного резерва 48.082 т</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -11419,7 +11563,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11432,7 +11576,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11612,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11481,7 +11625,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11530,7 +11674,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11710,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11579,7 +11723,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11759,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11628,7 +11772,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11808,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11677,7 +11821,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13563,6 +13707,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13618,6 +13767,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13673,6 +13827,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13728,6 +13887,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13783,6 +13947,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13838,6 +14007,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13893,6 +14067,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13948,6 +14127,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14003,6 +14187,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14058,6 +14247,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14113,6 +14307,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14168,6 +14367,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14223,6 +14427,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14278,6 +14487,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14333,6 +14547,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14388,6 +14607,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14443,6 +14667,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14498,6 +14727,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14553,6 +14787,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14608,6 +14847,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14663,6 +14907,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14718,6 +14967,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14773,6 +15027,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14828,6 +15087,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14883,6 +15147,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14938,6 +15207,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14993,6 +15267,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15048,6 +15327,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15103,6 +15387,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15158,6 +15447,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15213,6 +15507,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15268,6 +15567,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15323,6 +15627,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15378,6 +15687,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15433,6 +15747,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15488,6 +15807,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15543,6 +15867,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15598,6 +15927,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15653,6 +15987,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15708,6 +16047,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15763,6 +16107,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -15818,6 +16167,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15873,6 +16227,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15928,6 +16287,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15983,6 +16347,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16038,6 +16407,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16093,6 +16467,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16148,6 +16527,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16203,6 +16587,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16258,6 +16647,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16313,6 +16707,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16368,6 +16767,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16423,6 +16827,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16478,6 +16887,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16533,6 +16947,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16588,6 +17007,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16643,6 +17067,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16698,6 +17127,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16753,6 +17187,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16808,6 +17247,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16863,6 +17307,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16918,6 +17367,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16973,6 +17427,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17028,6 +17487,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17083,6 +17547,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17138,6 +17607,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17193,6 +17667,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17248,6 +17727,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17303,6 +17787,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17358,6 +17847,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17413,6 +17907,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17468,6 +17967,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17523,6 +18027,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17578,6 +18087,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17633,6 +18147,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17688,6 +18207,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17743,6 +18267,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17798,6 +18327,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17853,6 +18387,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17908,6 +18447,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17963,6 +18507,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18018,6 +18567,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18073,6 +18627,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18128,6 +18687,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18183,6 +18747,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18238,6 +18807,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18293,6 +18867,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18348,6 +18927,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18403,6 +18987,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18458,6 +19047,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18513,6 +19107,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18568,6 +19167,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18623,6 +19227,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18678,6 +19287,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18733,6 +19347,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18788,6 +19407,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18843,6 +19467,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18898,6 +19527,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18953,6 +19587,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19008,6 +19647,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19063,6 +19707,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19118,6 +19767,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19173,6 +19827,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19228,6 +19887,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19283,6 +19947,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19338,6 +20007,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19393,6 +20067,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19448,6 +20127,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19503,6 +20187,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19558,6 +20247,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -19613,6 +20307,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -19668,6 +20367,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -19723,6 +20427,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19778,6 +20487,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -19833,6 +20547,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -19888,6 +20607,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -19943,6 +20667,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19998,6 +20727,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20053,6 +20787,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20108,6 +20847,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20162,6 +20906,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1407,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11552,18 +11585,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11576,7 +11609,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11601,18 +11634,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11625,7 +11658,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11650,18 +11683,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11674,7 +11707,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11699,18 +11732,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11723,7 +11756,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11748,18 +11781,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11772,7 +11805,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11797,18 +11830,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11821,7 +11854,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11879,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -11870,7 +11903,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12114,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12105,7 +12138,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12349,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -12340,7 +12373,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12682,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -12673,7 +12706,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12982,7 +13015,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -13006,7 +13039,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13348,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -13339,7 +13372,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,6 +1439,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -7402,7 +7402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7511,6 +7511,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7586,6 +7591,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7661,6 +7669,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7736,6 +7747,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7811,6 +7825,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7886,6 +7903,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7961,6 +7981,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8036,6 +8059,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8111,6 +8137,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8186,6 +8215,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8261,6 +8293,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8336,6 +8371,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8411,6 +8449,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8486,6 +8527,9 @@
       <c r="U14" t="n">
         <v>2.50485</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8561,6 +8605,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8636,6 +8683,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8711,6 +8761,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8786,6 +8839,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8861,6 +8917,9 @@
       <c r="U19" t="n">
         <v>12.12255</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8936,6 +8995,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9011,6 +9073,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9086,6 +9151,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9161,6 +9229,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9236,6 +9307,9 @@
       <c r="U24" t="n">
         <v>16.5</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9311,6 +9385,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9386,6 +9463,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9461,6 +9541,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9536,6 +9619,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9611,6 +9697,9 @@
       <c r="U29" t="n">
         <v>16.5</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9686,6 +9775,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9761,6 +9853,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9834,6 +9929,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9848,7 +9946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9912,6 +10010,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9954,6 +10057,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9996,6 +10102,9 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10038,6 +10147,9 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10080,6 +10192,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10122,6 +10237,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10162,6 +10280,9 @@
         <v>1537.558975232535</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21056,7 +21177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21494,11 +21615,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -21514,11 +21635,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -21534,11 +21655,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -21554,11 +21675,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -21574,7 +21695,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -21594,10 +21715,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21614,11 +21735,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>71</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -21634,10 +21755,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>69</v>
       </c>
     </row>

--- a/results/alternatives/P1_earth_only_BASE/results.xlsx
+++ b/results/alternatives/P1_earth_only_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -734,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,7 +1260,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1278,24 +1280,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1305,29 +1307,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1337,29 +1339,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1369,176 +1371,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2275,6 +2420,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2347,6 +2502,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2418,6 +2579,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2489,6 +2656,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2560,6 +2733,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2631,6 +2810,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2702,6 +2887,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2773,6 +2964,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2844,6 +3041,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2915,6 +3118,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2986,6 +3195,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3057,6 +3272,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3128,6 +3349,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3199,6 +3426,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3270,6 +3503,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3341,6 +3580,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3412,6 +3657,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3483,6 +3734,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3554,6 +3811,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3625,6 +3888,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3696,6 +3965,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3767,6 +4042,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3838,6 +4119,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3909,6 +4196,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3980,6 +4273,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4051,6 +4350,12 @@
         <v>1.423987865000004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.87468750000008</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4122,6 +4427,12 @@
         <v>1.460974635000005</v>
       </c>
       <c r="U27" t="n">
+        <v>40.49113366666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4193,6 +4504,12 @@
         <v>1.497961405000004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.1075798333334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4264,6 +4581,12 @@
         <v>1.534948175000004</v>
       </c>
       <c r="U29" t="n">
+        <v>41.72402600000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4335,6 +4658,12 @@
         <v>1.571934945000004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.34047216666673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4406,6 +4735,12 @@
         <v>1.608921715000003</v>
       </c>
       <c r="U31" t="n">
+        <v>42.95691833333339</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4477,6 +4812,12 @@
         <v>1.645908485000003</v>
       </c>
       <c r="U32" t="n">
+        <v>43.57336450000005</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4548,6 +4889,12 @@
         <v>1.682895255000003</v>
       </c>
       <c r="U33" t="n">
+        <v>44.18981066666672</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4619,6 +4966,12 @@
         <v>1.719882025000002</v>
       </c>
       <c r="U34" t="n">
+        <v>44.80625683333338</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4690,6 +5043,12 @@
         <v>1.756868795000002</v>
       </c>
       <c r="U35" t="n">
+        <v>45.42270300000004</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4761,6 +5120,12 @@
         <v>1.793855565000002</v>
       </c>
       <c r="U36" t="n">
+        <v>46.0391491666667</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4832,6 +5197,12 @@
         <v>1.830842335000002</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65559533333337</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4903,6 +5274,12 @@
         <v>1.870911068750002</v>
       </c>
       <c r="U38" t="n">
+        <v>52.37477362500003</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4974,6 +5351,12 @@
         <v>1.914061766250002</v>
       </c>
       <c r="U39" t="n">
+        <v>53.0939519166667</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5045,6 +5428,12 @@
         <v>1.957212463750002</v>
       </c>
       <c r="U40" t="n">
+        <v>53.81313020833337</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5116,6 +5505,12 @@
         <v>2.000363161250002</v>
       </c>
       <c r="U41" t="n">
+        <v>54.53230850000003</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5187,6 +5582,12 @@
         <v>2.043513858750002</v>
       </c>
       <c r="U42" t="n">
+        <v>55.2514867916667</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5258,6 +5659,12 @@
         <v>2.086664556250002</v>
       </c>
       <c r="U43" t="n">
+        <v>55.97066508333337</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5329,6 +5736,12 @@
         <v>2.129815253750002</v>
       </c>
       <c r="U44" t="n">
+        <v>56.68984337500003</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5400,6 +5813,12 @@
         <v>2.172965951250001</v>
       </c>
       <c r="U45" t="n">
+        <v>57.4090216666667</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5471,6 +5890,12 @@
         <v>2.216116648750001</v>
       </c>
       <c r="U46" t="n">
+        <v>58.12819995833336</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5542,6 +5967,12 @@
         <v>2.259267346250001</v>
       </c>
       <c r="U47" t="n">
+        <v>58.84737825000003</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5613,6 +6044,12 @@
         <v>2.302418043750001</v>
       </c>
       <c r="U48" t="n">
+        <v>59.56655654166669</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5684,6 +6121,12 @@
         <v>2.345568741250001</v>
       </c>
       <c r="U49" t="n">
+        <v>60.28573483333336</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5755,6 +6198,12 @@
         <v>2.283394090000001</v>
       </c>
       <c r="U50" t="n">
+        <v>63.32740150000002</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5826,6 +6275,12 @@
         <v>2.115894090000001</v>
       </c>
       <c r="U51" t="n">
+        <v>60.53573483333335</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5897,6 +6352,12 @@
         <v>1.948394090000001</v>
       </c>
       <c r="U52" t="n">
+        <v>57.74406816666668</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5968,6 +6429,12 @@
         <v>1.78089409</v>
       </c>
       <c r="U53" t="n">
+        <v>54.95240150000001</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6039,6 +6506,12 @@
         <v>1.61339409</v>
       </c>
       <c r="U54" t="n">
+        <v>52.16073483333334</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6110,6 +6583,12 @@
         <v>1.44589409</v>
       </c>
       <c r="U55" t="n">
+        <v>49.36906816666666</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6181,6 +6660,12 @@
         <v>1.27839409</v>
       </c>
       <c r="U56" t="n">
+        <v>46.57740149999999</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6252,6 +6737,12 @@
         <v>1.110894089999999</v>
       </c>
       <c r="U57" t="n">
+        <v>43.78573483333332</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6323,6 +6814,12 @@
         <v>0.9433940899999991</v>
       </c>
       <c r="U58" t="n">
+        <v>40.99406816666665</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6394,6 +6891,12 @@
         <v>0.7758940899999988</v>
       </c>
       <c r="U59" t="n">
+        <v>38.20240149999998</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6465,6 +6968,12 @@
         <v>0.6083940899999986</v>
       </c>
       <c r="U60" t="n">
+        <v>35.41073483333331</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6536,6 +7045,12 @@
         <v>0.4408940899999982</v>
       </c>
       <c r="U61" t="n">
+        <v>32.61906816666664</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6607,6 +7122,12 @@
         <v>0.178572044999999</v>
       </c>
       <c r="U62" t="n">
+        <v>29.82740149999997</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6678,6 +7199,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6749,6 +7276,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6820,6 +7353,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6891,6 +7430,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6962,6 +7507,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7033,6 +7584,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7104,6 +7661,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7175,6 +7738,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7246,6 +7815,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7317,6 +7892,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7388,6 +7969,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>23.875</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10037,7 +10624,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10046,13 +10633,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10449,7 +11036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12140,7 +12727,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12148,14 +12735,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12172,7 +12759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12776,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12197,14 +12784,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12238,7 +12825,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12246,18 +12833,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -12267,7 +12855,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12282,7 +12874,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12290,7 +12882,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -12326,27 +12918,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -12356,11 +12947,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12375,7 +12962,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12383,14 +12970,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12407,7 +12994,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12424,7 +13011,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12432,14 +13019,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -12456,7 +13043,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12473,7 +13060,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12481,170 +13068,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>30.82226200000003</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12659,7 +13246,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12667,14 +13254,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>30.82226200000003</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -12691,7 +13278,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12708,7 +13295,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12716,14 +13303,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>16.699</v>
+        <v>46.65559533333337</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -12740,7 +13327,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12757,7 +13344,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12765,14 +13352,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>16.6988</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>16.699</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -12789,7 +13376,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -12806,7 +13393,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12814,219 +13401,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>16.6988</v>
+      </c>
+      <c r="G52" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>39.45240150000002</v>
-      </c>
-      <c r="G52" t="n">
-        <v>70</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" t="n">
-        <v>190</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13041,7 +13628,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13049,14 +13636,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>80.81699999999999</v>
+        <v>39.45240150000002</v>
       </c>
       <c r="G55" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -13073,7 +13660,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13677,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13098,14 +13685,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>80.8169</v>
+        <v>60.28573483333336</v>
       </c>
       <c r="G56" t="n">
-        <v>80.81699999999999</v>
+        <v>70</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -13122,7 +13709,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13726,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13147,268 +13734,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>190</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>190</v>
+      </c>
+      <c r="G58" t="n">
+        <v>190</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="G59" t="n">
+        <v>110</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>80.8169</v>
+      </c>
+      <c r="G60" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>36.66073483333335</v>
-      </c>
-      <c r="G59" t="n">
-        <v>70</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>110</v>
-      </c>
-      <c r="G62" t="n">
-        <v>110</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13423,7 +14010,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -13431,14 +14018,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>110</v>
+        <v>36.66073483333335</v>
       </c>
       <c r="G63" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -13455,7 +14042,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13472,7 +14059,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -13480,317 +14067,317 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>63.32740150000002</v>
+      </c>
+      <c r="G64" t="n">
+        <v>70</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2039-01, хранилище BASE; поставка одной партией в начале месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>190</v>
+      </c>
+      <c r="G65" t="n">
+        <v>190</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>110</v>
+      </c>
+      <c r="G67" t="n">
+        <v>110</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>110</v>
+      </c>
+      <c r="G68" t="n">
+        <v>110</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69">
         <f>=</f>
         <v/>
       </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D70" t="n">
         <v>2039</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65">
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70">
         <f>=</f>
         <v/>
       </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>70</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>190</v>
-      </c>
-      <c r="G67" t="n">
-        <v>190</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>190</v>
-      </c>
-      <c r="G68" t="n">
-        <v>190</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>110</v>
-      </c>
-      <c r="G69" t="n">
-        <v>110</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>110</v>
-      </c>
-      <c r="G70" t="n">
-        <v>110</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13805,7 +14392,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13813,72 +14400,366 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>end_of_month_stock_t_in_worst_month</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>70</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2040-01, хранилище BASE; проверка помесячная</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>29.82740149999997</v>
+      </c>
+      <c r="G72" t="n">
+        <v>70</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2040-01, хранилище BASE; поставка одной партией в начале месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>190</v>
+      </c>
+      <c r="G73" t="n">
+        <v>190</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>190</v>
+      </c>
+      <c r="G74" t="n">
+        <v>190</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>110</v>
+      </c>
+      <c r="G75" t="n">
+        <v>110</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>110</v>
+      </c>
+      <c r="G76" t="n">
+        <v>110</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77">
         <f>=</f>
         <v/>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P1_earth_only</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D78" t="n">
         <v>2040</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72">
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78">
         <f>=</f>
         <v/>
       </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21177,7 +22058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21219,7 +22100,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9879.471813385</v>
+        <v>9879.841679155001</v>
       </c>
     </row>
     <row r="3">
@@ -21239,7 +22120,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7857.379987037734</v>
+        <v>7857.749852807734</v>
       </c>
     </row>
     <row r="4">
@@ -21379,7 +22260,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.643973427508077</v>
+        <v>7.644259601118472</v>
       </c>
     </row>
     <row r="11">
@@ -21399,7 +22280,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.079434707164908</v>
+        <v>6.079720880775302</v>
       </c>
     </row>
     <row r="12">
@@ -21559,7 +22440,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>86.65103338500009</v>
+        <v>87.02089915500009</v>
       </c>
     </row>
     <row r="20">
@@ -21675,11 +22556,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -21695,11 +22576,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -21715,11 +22596,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -21735,10 +22616,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21755,11 +22636,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -21775,11 +22656,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P1_earth_only</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>69</v>
+      <c r="D32" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
